--- a/diseases/d011/2005-2009.xlsx
+++ b/diseases/d011/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2149,9 +2143,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2989,9 +2980,6 @@
       <c r="O15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -3829,9 +3817,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -4669,9 +4654,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5509,9 +5491,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6349,9 +6328,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7041,9 +7017,6 @@
       <c r="O39" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -7881,9 +7854,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -8721,9 +8691,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9561,9 +9528,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -10401,9 +10365,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -11093,9 +11054,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11637,9 +11595,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12329,9 +12284,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13169,9 +13121,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14009,9 +13958,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14849,9 +14795,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -15689,9 +15632,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -16381,9 +16321,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17221,9 +17158,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17913,9 +17847,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18605,9 +18536,6 @@
       <c r="O107" t="n">
         <v>3</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -19445,9 +19373,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -20137,9 +20062,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -20829,9 +20751,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21373,9 +21292,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22065,9 +21981,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -22757,9 +22670,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23597,9 +23507,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -24437,9 +24344,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -25277,9 +25181,6 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -25969,9 +25870,6 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -26661,9 +26559,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -27353,9 +27248,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -28193,9 +28085,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -29033,9 +28922,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -29873,9 +29759,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -30713,9 +30596,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -31257,9 +31137,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -31801,9 +31678,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -32641,9 +32515,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -33333,9 +33204,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -34173,9 +34041,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -35013,9 +34878,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -35853,9 +35715,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -36693,9 +36552,6 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -37533,9 +37389,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -38373,9 +38226,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -39213,9 +39063,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -39905,9 +39752,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -40597,9 +40441,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -41141,9 +40982,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -41833,9 +41671,6 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -42673,9 +42508,6 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -43365,9 +43197,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -44057,9 +43886,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -44897,9 +44723,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -45589,9 +45412,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -46281,9 +46101,6 @@
       <c r="O269" t="n">
         <v>1</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -47121,9 +46938,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -47961,9 +47775,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -48801,9 +48612,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -49491,9 +49299,6 @@
         <v>0</v>
       </c>
       <c r="O288" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
